--- a/output/yearly_surface_area_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_9_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497641925596</v>
+        <v>10.84497611103198</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907224520153</v>
+        <v>37.7890711712021</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.002986300841745</v>
+        <v>8.663923489978101</v>
       </c>
       <c r="C2" t="n">
-        <v>11.64549126777566</v>
+        <v>5.6941366846315</v>
       </c>
       <c r="D2" t="n">
-        <v>30.89854549575987</v>
+        <v>26.27942254727862</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.73955912093411</v>
+        <v>25.01984024272996</v>
       </c>
       <c r="C3" t="n">
-        <v>27.58711048933537</v>
+        <v>25.69233742013903</v>
       </c>
       <c r="D3" t="n">
-        <v>89.35376730202346</v>
+        <v>57.87402716534947</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.83549265850982</v>
+        <v>45.58843639440489</v>
       </c>
       <c r="C4" t="n">
-        <v>76.58908365140641</v>
+        <v>82.74071476621694</v>
       </c>
       <c r="D4" t="n">
-        <v>108.7000875619111</v>
+        <v>67.39992513965628</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.32466505713199</v>
+        <v>54.38882281527331</v>
       </c>
       <c r="C5" t="n">
-        <v>119.8713946885356</v>
+        <v>114.7663066264522</v>
       </c>
       <c r="D5" t="n">
-        <v>79.10432126968676</v>
+        <v>48.37561812676159</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.05290086950487</v>
+        <v>51.03909964838319</v>
       </c>
       <c r="C6" t="n">
-        <v>129.3688219794192</v>
+        <v>82.55614619781855</v>
       </c>
       <c r="D6" t="n">
-        <v>50.51582812201963</v>
+        <v>38.80259626265094</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.71509754378595</v>
+        <v>37.72856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>101.507803880599</v>
+        <v>62.34196096737671</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>37.84833749412304</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.51728322914683</v>
+        <v>19.86075605691297</v>
       </c>
       <c r="C8" t="n">
-        <v>69.9298889735003</v>
+        <v>41.14013754646259</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>9.096874227550941</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82187136383736</v>
+        <v>29.84218496599028</v>
       </c>
       <c r="D9" t="n">
-        <v>33.83593462686631</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.67936861405344</v>
+        <v>7.733361820783536</v>
       </c>
       <c r="C21" t="n">
-        <v>93.11234444539797</v>
+        <v>96.66702275979421</v>
       </c>
       <c r="D21" t="n">
-        <v>7.67936861405344</v>
+        <v>8.700032048381479</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.227806525114265</v>
+        <v>9.552405162321465</v>
       </c>
       <c r="C2" t="n">
-        <v>7.449501579824798</v>
+        <v>7.387651474457248</v>
       </c>
       <c r="D2" t="n">
-        <v>30.97708531209961</v>
+        <v>23.00333045820701</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.10909716835841</v>
+        <v>27.05205799052086</v>
       </c>
       <c r="C3" t="n">
-        <v>36.32957379565322</v>
+        <v>23.67975462643307</v>
       </c>
       <c r="D3" t="n">
-        <v>92.20574438286043</v>
+        <v>64.47628047640927</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.69961056469625</v>
+        <v>46.3541996037174</v>
       </c>
       <c r="C4" t="n">
-        <v>71.96897895522092</v>
+        <v>73.05381016841365</v>
       </c>
       <c r="D4" t="n">
-        <v>125.5596408869416</v>
+        <v>79.7031873692773</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.04901493641689</v>
+        <v>61.01561981893928</v>
       </c>
       <c r="C5" t="n">
-        <v>130.0079397348839</v>
+        <v>132.5604837659256</v>
       </c>
       <c r="D5" t="n">
-        <v>95.89220701230721</v>
+        <v>59.69026041820608</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.73467574460867</v>
+        <v>62.55107322838128</v>
       </c>
       <c r="C6" t="n">
-        <v>156.5386896944497</v>
+        <v>131.3814047731252</v>
       </c>
       <c r="D6" t="n">
-        <v>61.98755004614362</v>
+        <v>44.88059629964295</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.32069700858599</v>
+        <v>48.92736033654828</v>
       </c>
       <c r="C7" t="n">
-        <v>141.571945943207</v>
+        <v>89.53048188878788</v>
       </c>
       <c r="D7" t="n">
-        <v>44.37597797966008</v>
+        <v>40.18391528252619</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.60902773399829</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="C8" t="n">
-        <v>99.30378028456487</v>
+        <v>61.66848204226339</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>14.42187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>63.34530712111692</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>40.14366362665208</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.856398699403767</v>
+        <v>7.923120258822921</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1511332548235</v>
+        <v>105.9717334617566</v>
       </c>
       <c r="D21" t="n">
-        <v>8.838448536829238</v>
+        <v>9.903900323528651</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.551202430438965</v>
+        <v>10.60680219668254</v>
       </c>
       <c r="C2" t="n">
-        <v>11.1261467322291</v>
+        <v>9.261807841864409</v>
       </c>
       <c r="D2" t="n">
-        <v>26.5788555970739</v>
+        <v>22.41526358336318</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.84540794654352</v>
+        <v>29.10881943091793</v>
       </c>
       <c r="C3" t="n">
-        <v>32.58911504247288</v>
+        <v>26.00158794697677</v>
       </c>
       <c r="D3" t="n">
-        <v>93.82562809486768</v>
+        <v>66.714665242092</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.94210224764522</v>
+        <v>48.4472857091716</v>
       </c>
       <c r="C4" t="n">
-        <v>80.17540801502001</v>
+        <v>66.23851760553229</v>
       </c>
       <c r="D4" t="n">
-        <v>136.969512705698</v>
+        <v>90.01546525468579</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.19627709205391</v>
+        <v>64.37810570598461</v>
       </c>
       <c r="C5" t="n">
-        <v>129.5170658827605</v>
+        <v>132.0205225285899</v>
       </c>
       <c r="D5" t="n">
-        <v>113.9318210778424</v>
+        <v>72.23208733995908</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.52462279362885</v>
+        <v>71.16492758544281</v>
       </c>
       <c r="C6" t="n">
-        <v>176.4632593521387</v>
+        <v>167.2858818128395</v>
       </c>
       <c r="D6" t="n">
-        <v>73.37876865851936</v>
+        <v>51.4818678629985</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.38731698375453</v>
+        <v>60.30581622876881</v>
       </c>
       <c r="C7" t="n">
-        <v>178.1626646281899</v>
+        <v>133.2477071588984</v>
       </c>
       <c r="D7" t="n">
-        <v>50.48441219548373</v>
+        <v>43.6573386601514</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.11801501315464</v>
+        <v>40.55599766243574</v>
       </c>
       <c r="C8" t="n">
-        <v>135.6873502039516</v>
+        <v>87.53753404916685</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.20156137900685</v>
+        <v>21.1890607007589</v>
       </c>
       <c r="C9" t="n">
-        <v>88.19530501101218</v>
+        <v>56.13437023342411</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>54.94841900669398</v>
+        <v>39.85895679242051</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>35.89465956267188</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>36.01639627799849</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>19.26188995732242</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>11.43245201595411</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.017375852280837</v>
+        <v>8.097023844787531</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2367459873264</v>
+        <v>114.3704618076239</v>
       </c>
       <c r="D21" t="n">
-        <v>10.02171981535105</v>
+        <v>11.13340778658285</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.948409340031424</v>
+        <v>9.689849840916018</v>
       </c>
       <c r="C2" t="n">
-        <v>7.65468685001238</v>
+        <v>6.14966761940202</v>
       </c>
       <c r="D2" t="n">
-        <v>22.16295442337174</v>
+        <v>18.26443428980766</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.81519475189012</v>
+        <v>34.71950756068845</v>
       </c>
       <c r="C3" t="n">
-        <v>50.24093876483052</v>
+        <v>41.28249096357838</v>
       </c>
       <c r="D3" t="n">
-        <v>101.7483320681394</v>
+        <v>72.68369128391261</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.82501222893259</v>
+        <v>30.92407093607028</v>
       </c>
       <c r="C4" t="n">
-        <v>108.5214094797382</v>
+        <v>103.4163214176548</v>
       </c>
       <c r="D4" t="n">
-        <v>130.3584236653</v>
+        <v>85.21668247632739</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.64815877344793</v>
+        <v>40.07985002587604</v>
       </c>
       <c r="C5" t="n">
-        <v>105.4397034361075</v>
+        <v>99.94191629232532</v>
       </c>
       <c r="D5" t="n">
-        <v>74.46556336712058</v>
+        <v>50.85453107998479</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.82898027747859</v>
+        <v>37.43403996293088</v>
       </c>
       <c r="C6" t="n">
-        <v>117.3335768730576</v>
+        <v>87.74860980557993</v>
       </c>
       <c r="D6" t="n">
-        <v>33.24786775202249</v>
+        <v>28.73968229412113</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>26.88908787161589</v>
       </c>
       <c r="C7" t="n">
-        <v>95.39936966477529</v>
+        <v>61.56343503790898</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>28.02693346083794</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="C8" t="n">
-        <v>65.00642423670254</v>
+        <v>41.30703465618455</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>41.93437143919824</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>9.628981483252716</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.50582105186536</v>
+        <v>5.830599615521806</v>
       </c>
       <c r="C2" t="n">
-        <v>3.496003574822891</v>
+        <v>3.244676162535709</v>
       </c>
       <c r="D2" t="n">
-        <v>16.05942894606932</v>
+        <v>13.544191327789</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.09637550593221</v>
+        <v>35.21038141281186</v>
       </c>
       <c r="C3" t="n">
-        <v>40.69344234103029</v>
+        <v>32.84927818409827</v>
       </c>
       <c r="D3" t="n">
-        <v>98.0962306083413</v>
+        <v>71.7608484419206</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.35501712050563</v>
+        <v>46.91575929054657</v>
       </c>
       <c r="C4" t="n">
-        <v>120.6077054667207</v>
+        <v>106.122018090559</v>
       </c>
       <c r="D4" t="n">
-        <v>146.9627225872263</v>
+        <v>99.37053912845366</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.00435326364027</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="C5" t="n">
-        <v>149.9374181310941</v>
+        <v>145.3968349989526</v>
       </c>
       <c r="D5" t="n">
-        <v>95.62222639363934</v>
+        <v>65.9489020327795</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.29691407950582</v>
+        <v>45.36361617013237</v>
       </c>
       <c r="C6" t="n">
-        <v>142.0078419238926</v>
+        <v>120.8354709341059</v>
       </c>
       <c r="D6" t="n">
-        <v>42.34474197957343</v>
+        <v>34.45541742824607</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.57051858935441</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>124.6839219347534</v>
+        <v>85.93728529124455</v>
       </c>
       <c r="D7" t="n">
-        <v>31.56024344842221</v>
+        <v>30.24273802932299</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.844164156932015</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="C8" t="n">
-        <v>85.03407740333748</v>
+        <v>55.7436346471339</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>46.92655851529327</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.69185439405351</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>8.025787482217675</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.012983704333461</v>
+        <v>5.942518853805943</v>
       </c>
       <c r="C2" t="n">
-        <v>5.125704763872597</v>
+        <v>11.76035574917254</v>
       </c>
       <c r="D2" t="n">
-        <v>18.31450342272425</v>
+        <v>17.36220814960484</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.98776136365931</v>
+        <v>27.36130851735861</v>
       </c>
       <c r="C3" t="n">
-        <v>26.66426764734337</v>
+        <v>21.82916020392783</v>
       </c>
       <c r="D3" t="n">
-        <v>89.07887794483435</v>
+        <v>66.23851760553229</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.16205479112551</v>
+        <v>57.52157973952487</v>
       </c>
       <c r="C4" t="n">
-        <v>110.9846144696934</v>
+        <v>93.37206065550565</v>
       </c>
       <c r="D4" t="n">
-        <v>160.1338497874015</v>
+        <v>111.4185469549705</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.20761609614836</v>
+        <v>57.01499792413352</v>
       </c>
       <c r="C5" t="n">
-        <v>184.5931120910065</v>
+        <v>172.4930716361646</v>
       </c>
       <c r="D5" t="n">
-        <v>121.4176473227243</v>
+        <v>84.3566714874072</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.60384125803657</v>
+        <v>52.97117913034091</v>
       </c>
       <c r="C6" t="n">
-        <v>187.8947296203886</v>
+        <v>173.8066500644468</v>
       </c>
       <c r="D6" t="n">
-        <v>58.24414604985053</v>
+        <v>45.28311285838414</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.75691178444107</v>
+        <v>37.60879105428681</v>
       </c>
       <c r="C7" t="n">
-        <v>161.0949807898591</v>
+        <v>128.9957578518054</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>18.10833640483241</v>
       </c>
       <c r="C8" t="n">
-        <v>121.4176473227242</v>
+        <v>83.19820919639595</v>
       </c>
       <c r="D8" t="n">
-        <v>29.54078842078653</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>72.44218134866787</v>
+        <v>51.47499562906875</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>3.131775176547325</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>37.43894870145212</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.7483380970101</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>15.29268398905256</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.801507037292897</v>
+        <v>3.534291735288517</v>
       </c>
       <c r="C2" t="n">
-        <v>2.447497026687298</v>
+        <v>5.300455855228529</v>
       </c>
       <c r="D2" t="n">
-        <v>12.8059170541954</v>
+        <v>11.97732199181109</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2219981543468</v>
+        <v>26.94406574305371</v>
       </c>
       <c r="C3" t="n">
-        <v>25.55489274154447</v>
+        <v>34.10591524553419</v>
       </c>
       <c r="D3" t="n">
-        <v>87.3411845083175</v>
+        <v>66.95028469111124</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.35273482992764</v>
+        <v>63.30309196983433</v>
       </c>
       <c r="C4" t="n">
-        <v>106.122018090559</v>
+        <v>87.73093834690347</v>
       </c>
       <c r="D4" t="n">
-        <v>169.7314153441183</v>
+        <v>119.2038062496477</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.70478134512475</v>
+        <v>59.07666810305183</v>
       </c>
       <c r="C5" t="n">
-        <v>218.095252498429</v>
+        <v>199.5156771955581</v>
       </c>
       <c r="D5" t="n">
-        <v>128.0689880189964</v>
+        <v>91.91612881010764</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.04911274740813</v>
+        <v>45.36361617013237</v>
       </c>
       <c r="C6" t="n">
-        <v>222.6319086397535</v>
+        <v>208.8658423308047</v>
       </c>
       <c r="D6" t="n">
-        <v>56.63407981488576</v>
+        <v>45.12210623488766</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="C7" t="n">
-        <v>164.6881773874024</v>
+        <v>126.420633623566</v>
       </c>
       <c r="D7" t="n">
-        <v>35.2133266559246</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>90.20788780471817</v>
+        <v>64.83952712698058</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.919578803709772</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>6.138868394655306</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.351285751671111</v>
+        <v>4.828235209485814</v>
       </c>
       <c r="C2" t="n">
-        <v>5.571418221600648</v>
+        <v>6.563965150594174</v>
       </c>
       <c r="D2" t="n">
-        <v>20.56761440397068</v>
+        <v>14.28835608760808</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.92194320974577</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="C3" t="n">
-        <v>17.55364895193297</v>
+        <v>27.06678420608456</v>
       </c>
       <c r="D3" t="n">
-        <v>79.13868243933538</v>
+        <v>61.48685871697774</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.39178375391926</v>
+        <v>57.84064774340508</v>
       </c>
       <c r="C4" t="n">
-        <v>85.62508952129406</v>
+        <v>87.20766682053993</v>
       </c>
       <c r="D4" t="n">
-        <v>173.3687905883527</v>
+        <v>124.5258605543697</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.38695713085605</v>
+        <v>74.93189352663781</v>
       </c>
       <c r="C5" t="n">
-        <v>209.455872701057</v>
+        <v>183.071403149424</v>
       </c>
       <c r="D5" t="n">
-        <v>152.7353990881975</v>
+        <v>110.2011798017045</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.77743067523902</v>
+        <v>59.69320566131882</v>
       </c>
       <c r="C6" t="n">
-        <v>278.5414586489051</v>
+        <v>260.0659486026844</v>
       </c>
       <c r="D6" t="n">
-        <v>76.47814616082654</v>
+        <v>60.17622553180826</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.97165248976386</v>
+        <v>26.05067533218911</v>
       </c>
       <c r="C7" t="n">
-        <v>233.0786859606437</v>
+        <v>204.6924328400515</v>
       </c>
       <c r="D7" t="n">
-        <v>41.44153409166636</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>141.0280577150543</v>
+        <v>107.4817386609408</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4609323660398</v>
+        <v>48.47968338341173</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.590431280879833</v>
+        <v>3.632466505713198</v>
       </c>
       <c r="C2" t="n">
-        <v>3.178899066351172</v>
+        <v>4.557272843113694</v>
       </c>
       <c r="D2" t="n">
-        <v>14.43758173865359</v>
+        <v>10.52433538952581</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.802750826904402</v>
+        <v>18.53539665617978</v>
       </c>
       <c r="C3" t="n">
-        <v>19.74785507092459</v>
+        <v>26.8851608807989</v>
       </c>
       <c r="D3" t="n">
-        <v>78.43673283079892</v>
+        <v>59.33192250615598</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.53744226704628</v>
+        <v>51.47205038595602</v>
       </c>
       <c r="C4" t="n">
-        <v>69.74826564821464</v>
+        <v>80.11159441424397</v>
       </c>
       <c r="D4" t="n">
-        <v>173.8027230736298</v>
+        <v>126.6827602605999</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.11759840699392</v>
+        <v>81.33779729684825</v>
       </c>
       <c r="C5" t="n">
-        <v>197.2085700905781</v>
+        <v>180.5188591183823</v>
       </c>
       <c r="D5" t="n">
-        <v>168.6151682043897</v>
+        <v>123.8474728907351</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.65417243286043</v>
+        <v>71.60769580005812</v>
       </c>
       <c r="C6" t="n">
-        <v>309.6559886395993</v>
+        <v>283.6936706007924</v>
       </c>
       <c r="D6" t="n">
-        <v>92.82031844571895</v>
+        <v>71.04417261782045</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.47448724078747</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="C7" t="n">
-        <v>291.5879038906409</v>
+        <v>265.0581356787793</v>
       </c>
       <c r="D7" t="n">
-        <v>46.47200932822701</v>
+        <v>41.86074036137975</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>182.5854380358218</v>
+        <v>147.9542877685155</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>69.11405663127118</v>
+        <v>58.79687000734145</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>32.02951885105219</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>7.525096153051802</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.6467918106494</v>
+        <v>5.738315331322607</v>
       </c>
       <c r="C2" t="n">
-        <v>6.600289815651307</v>
+        <v>12.06077054667207</v>
       </c>
       <c r="D2" t="n">
-        <v>15.48805178219768</v>
+        <v>12.13832861530756</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.716536955379929</v>
+        <v>15.4821612959722</v>
       </c>
       <c r="C3" t="n">
-        <v>16.40009539944297</v>
+        <v>22.39366513386975</v>
       </c>
       <c r="D3" t="n">
-        <v>72.66405632982767</v>
+        <v>54.72752577323844</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.87904941039517</v>
+        <v>43.72507925174444</v>
       </c>
       <c r="C4" t="n">
-        <v>60.69949705817179</v>
+        <v>74.0237769002095</v>
       </c>
       <c r="D4" t="n">
-        <v>172.8455190619892</v>
+        <v>126.7976247419968</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.25856916577796</v>
+        <v>79.76700097005336</v>
       </c>
       <c r="C5" t="n">
-        <v>168.2715565079033</v>
+        <v>165.8417309398925</v>
       </c>
       <c r="D5" t="n">
-        <v>185.7466656434966</v>
+        <v>134.9903093339364</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.38249036069132</v>
+        <v>86.38005350585986</v>
       </c>
       <c r="C6" t="n">
-        <v>312.2320946155429</v>
+        <v>286.1087699532395</v>
       </c>
       <c r="D6" t="n">
-        <v>114.5562126177433</v>
+        <v>87.86936477320229</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>45.27427712904591</v>
       </c>
       <c r="C7" t="n">
-        <v>352.7920192687955</v>
+        <v>324.9447456378347</v>
       </c>
       <c r="D7" t="n">
-        <v>56.77250624118454</v>
+        <v>49.52622643613884</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.176575718044183</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>261.0270796051419</v>
+        <v>229.5669744225529</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>123.473427015417</v>
+        <v>105.2796785603152</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>48.9695754878309</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>12.29148125717007</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>7.166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.390375733391736</v>
+        <v>7.355253800217104</v>
       </c>
       <c r="C2" t="n">
-        <v>8.144578954431539</v>
+        <v>2.952115346670159</v>
       </c>
       <c r="D2" t="n">
-        <v>9.283406291357839</v>
+        <v>6.039711876526377</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.91146278016854</v>
+        <v>4.108614142272901</v>
       </c>
       <c r="C2" t="n">
-        <v>3.80132711084365</v>
+        <v>6.849653732529996</v>
       </c>
       <c r="D2" t="n">
-        <v>11.52277280474481</v>
+        <v>8.932922360941728</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.60287520586555</v>
+        <v>21.01430960940298</v>
       </c>
       <c r="C3" t="n">
-        <v>21.55917958525995</v>
+        <v>33.11925880276615</v>
       </c>
       <c r="D3" t="n">
-        <v>78.55945129382977</v>
+        <v>59.69516915672731</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.92331017254428</v>
+        <v>60.63568345739575</v>
       </c>
       <c r="C4" t="n">
-        <v>90.07927885546184</v>
+        <v>103.6971012610693</v>
       </c>
       <c r="D4" t="n">
-        <v>177.4911491984851</v>
+        <v>129.3756942133489</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.07798434145878</v>
+        <v>50.85453107998479</v>
       </c>
       <c r="C5" t="n">
-        <v>259.3531997694012</v>
+        <v>245.0196832873978</v>
       </c>
       <c r="D5" t="n">
-        <v>167.9524885040231</v>
+        <v>124.7310458245573</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.17487426454295</v>
+        <v>28.09565580013523</v>
       </c>
       <c r="C6" t="n">
-        <v>290.4962004435185</v>
+        <v>270.0886109153401</v>
       </c>
       <c r="D6" t="n">
-        <v>88.63414623481054</v>
+        <v>71.40643752068752</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.73104218676538</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>183.5524595245049</v>
+        <v>161.3944138396544</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>90.95892479846698</v>
+        <v>77.60715602071035</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>25.2849121228766</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>37.38593432542277</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>10.14636252339079</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>5.838453597155781</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.412375093512666</v>
+        <v>8.055239913345078</v>
       </c>
       <c r="C2" t="n">
-        <v>3.967242472861361</v>
+        <v>1.941896959000191</v>
       </c>
       <c r="D2" t="n">
-        <v>20.36733787230433</v>
+        <v>6.310674242898497</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.331511928865933</v>
+        <v>15.61960597456675</v>
       </c>
       <c r="C3" t="n">
-        <v>20.52343575727957</v>
+        <v>7.554548584179206</v>
       </c>
       <c r="D3" t="n">
-        <v>10.93176068678823</v>
+        <v>8.452847733565036</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39825634085749</v>
+        <v>13.39919723595008</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14381260801864</v>
+        <v>70.14873847056219</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576265451865587</v>
+        <v>1.576376145405892</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.870049450140927</v>
+        <v>4.910702016642545</v>
       </c>
       <c r="C2" t="n">
-        <v>5.393721887131976</v>
+        <v>5.070726892434775</v>
       </c>
       <c r="D2" t="n">
-        <v>33.08293413770902</v>
+        <v>9.208793465835081</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93238258159398</v>
+        <v>23.27232932917064</v>
       </c>
       <c r="C3" t="n">
-        <v>17.36220814960484</v>
+        <v>7.569274799742908</v>
       </c>
       <c r="D3" t="n">
-        <v>25.39781310886498</v>
+        <v>11.70734137314322</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.97593933347934</v>
+        <v>18.07201173977529</v>
       </c>
       <c r="C4" t="n">
-        <v>31.83022406709009</v>
+        <v>12.23944862884498</v>
       </c>
       <c r="D4" t="n">
-        <v>20.80323385298991</v>
+        <v>19.50143639715864</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
         <v>36.80081269369168</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5008,7 +5008,7 @@
         <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44108113720378</v>
+        <v>15.44646262624982</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14497897597899</v>
+        <v>86.17500202013056</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250753923621849</v>
+        <v>3.251886868684172</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.224460371374025</v>
+        <v>5.419247327442394</v>
       </c>
       <c r="C2" t="n">
-        <v>6.620906517440489</v>
+        <v>3.908337610606552</v>
       </c>
       <c r="D2" t="n">
-        <v>24.78618428911922</v>
+        <v>11.96455927165588</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.07335334037803</v>
+        <v>19.73312885536089</v>
       </c>
       <c r="C3" t="n">
-        <v>19.5613230071177</v>
+        <v>15.07473599870977</v>
       </c>
       <c r="D3" t="n">
-        <v>45.9703362513569</v>
+        <v>16.35591675275186</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.16059001733575</v>
+        <v>33.78292025083699</v>
       </c>
       <c r="C4" t="n">
-        <v>38.69656751059227</v>
+        <v>16.25970547773567</v>
       </c>
       <c r="D4" t="n">
-        <v>28.84374755077129</v>
+        <v>20.81599657314512</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.964739198105127</v>
+        <v>15.70796326794897</v>
       </c>
       <c r="C5" t="n">
-        <v>35.80924751240241</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D5" t="n">
-        <v>30.13965452037709</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.51451791248334</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.82369599052563</v>
       </c>
     </row>
     <row r="11">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.09685853201771</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5319,10 +5319,10 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.95035713990669</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>32.1031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73293581271859</v>
+        <v>16.74887760281566</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0709084575834</v>
+        <v>102.1681533771755</v>
       </c>
       <c r="D21" t="n">
-        <v>4.183233953179647</v>
+        <v>5.024663280844698</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.98924183298229</v>
+        <v>6.615016031215008</v>
       </c>
       <c r="C2" t="n">
-        <v>12.41223622479242</v>
+        <v>7.358199043329844</v>
       </c>
       <c r="D2" t="n">
-        <v>28.54333275327177</v>
+        <v>23.20458873757761</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.29424657383356</v>
+        <v>19.1440802328128</v>
       </c>
       <c r="C3" t="n">
-        <v>23.09070600388498</v>
+        <v>15.28581175512284</v>
       </c>
       <c r="D3" t="n">
-        <v>54.58026361760142</v>
+        <v>22.28567288640259</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.56823629877643</v>
+        <v>36.51414236405162</v>
       </c>
       <c r="C4" t="n">
-        <v>44.42702886028091</v>
+        <v>28.30771330425253</v>
       </c>
       <c r="D4" t="n">
-        <v>44.50360518121217</v>
+        <v>23.94286301117121</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.73942025221387</v>
+        <v>33.4285093296039</v>
       </c>
       <c r="C5" t="n">
-        <v>54.73243451175969</v>
+        <v>23.58648859452962</v>
       </c>
       <c r="D5" t="n">
-        <v>33.30579086657305</v>
+        <v>30.75324683553134</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.821404033285093</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="C6" t="n">
-        <v>35.74347041621788</v>
+        <v>18.79752329321368</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.84054026575129</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.97185777840888</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.50155957034565</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>46.09305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>37.91411459030757</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05824723461987</v>
+        <v>18.08992283736101</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8085652925201</v>
+        <v>118.0152108913551</v>
       </c>
       <c r="D21" t="n">
-        <v>6.019415744873289</v>
+        <v>6.891399176137526</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.691772278595507</v>
+        <v>7.444592841303563</v>
       </c>
       <c r="C2" t="n">
-        <v>7.029313562407163</v>
+        <v>13.46957850226624</v>
       </c>
       <c r="D2" t="n">
-        <v>30.7021959549105</v>
+        <v>24.5780537758189</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1273494641116</v>
+        <v>19.06063167795183</v>
       </c>
       <c r="C3" t="n">
-        <v>35.22510762837555</v>
+        <v>21.84388641949153</v>
       </c>
       <c r="D3" t="n">
-        <v>60.33821390300897</v>
+        <v>33.61013265488955</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.02921575141593</v>
+        <v>27.10801760966293</v>
       </c>
       <c r="C4" t="n">
-        <v>43.43153668817465</v>
+        <v>28.60125586782233</v>
       </c>
       <c r="D4" t="n">
-        <v>53.15672944644354</v>
+        <v>25.95937279569416</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.79417713947344</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="C5" t="n">
-        <v>51.19814277647117</v>
+        <v>29.28062527916113</v>
       </c>
       <c r="D5" t="n">
-        <v>33.20761609614836</v>
+        <v>26.43355693684537</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.30442390377452</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="C6" t="n">
-        <v>42.42524529132167</v>
+        <v>19.68305972244431</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>30.14849024971531</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>23.41566449399068</v>
+        <v>15.69029180927252</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>22.2984356065578</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.057337541756576</v>
+        <v>7.07695771014859</v>
       </c>
       <c r="C21" t="n">
-        <v>66.1625394539679</v>
+        <v>67.23109824641159</v>
       </c>
       <c r="D21" t="n">
-        <v>4.41083596359786</v>
+        <v>5.307718282611442</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.833724785083795</v>
+        <v>7.620325680363742</v>
       </c>
       <c r="C2" t="n">
-        <v>8.296749848589794</v>
+        <v>6.908558594784804</v>
       </c>
       <c r="D2" t="n">
-        <v>33.03581024790517</v>
+        <v>21.93911594680347</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.59997102048182</v>
+        <v>23.6846633649543</v>
       </c>
       <c r="C3" t="n">
-        <v>30.22310307523806</v>
+        <v>42.89746593706438</v>
       </c>
       <c r="D3" t="n">
-        <v>71.54977268550753</v>
+        <v>46.79500432292422</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.5299481383108</v>
+        <v>34.07646281440679</v>
       </c>
       <c r="C4" t="n">
-        <v>71.64991095134071</v>
+        <v>45.32041927114551</v>
       </c>
       <c r="D4" t="n">
-        <v>71.93069079475531</v>
+        <v>38.1350078237631</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.27371198750239</v>
+        <v>35.9074222828271</v>
       </c>
       <c r="C5" t="n">
-        <v>69.04140730115695</v>
+        <v>44.47317100238052</v>
       </c>
       <c r="D5" t="n">
-        <v>46.09305471438775</v>
+        <v>30.09056713516474</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.15349679922777</v>
+        <v>28.73968229412113</v>
       </c>
       <c r="C6" t="n">
-        <v>65.40894079544375</v>
+        <v>36.26674194258143</v>
       </c>
       <c r="D6" t="n">
-        <v>35.13969557810609</v>
+        <v>32.36233132279187</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>14.3727863901733</v>
       </c>
       <c r="C7" t="n">
-        <v>45.33416373900496</v>
+        <v>23.65521093382689</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>33.65627479698915</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>26.28629478120835</v>
+        <v>20.27799883121787</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
         <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.28437234352885</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.278707581661712</v>
+        <v>7.308312027015857</v>
       </c>
       <c r="C21" t="n">
-        <v>75.51659115974027</v>
+        <v>77.65081528704347</v>
       </c>
       <c r="D21" t="n">
-        <v>5.459030686246284</v>
+        <v>6.394773023638875</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.913246349127786</v>
+        <v>7.200137662946108</v>
       </c>
       <c r="C2" t="n">
-        <v>6.279258316362599</v>
+        <v>5.311255079975244</v>
       </c>
       <c r="D2" t="n">
-        <v>35.1338050918806</v>
+        <v>20.98878416909256</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28933783531232</v>
+        <v>25.43217427851362</v>
       </c>
       <c r="C3" t="n">
-        <v>31.76444697090555</v>
+        <v>32.91309178487432</v>
       </c>
       <c r="D3" t="n">
-        <v>81.37706720501812</v>
+        <v>53.91758391723482</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.00140802052752</v>
+        <v>41.555416825359</v>
       </c>
       <c r="C4" t="n">
-        <v>73.32182729167303</v>
+        <v>83.1491218111836</v>
       </c>
       <c r="D4" t="n">
-        <v>91.64909343455248</v>
+        <v>53.80762817435918</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.99868376159304</v>
+        <v>44.59588946541137</v>
       </c>
       <c r="C5" t="n">
-        <v>105.2188102026519</v>
+        <v>67.27426143351269</v>
       </c>
       <c r="D5" t="n">
-        <v>61.06470720415162</v>
+        <v>37.47821860962199</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.28433128579986</v>
+        <v>40.45291415348983</v>
       </c>
       <c r="C6" t="n">
-        <v>89.88194756690825</v>
+        <v>56.23156325614456</v>
       </c>
       <c r="D6" t="n">
-        <v>42.02272873258048</v>
+        <v>34.65667570761666</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C7" t="n">
-        <v>71.86393195086652</v>
+        <v>40.24380189248525</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>45.06221962492859</v>
+        <v>26.95388322009618</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>28.95468504135117</v>
+        <v>25.18281036163492</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.67484588791184</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>22.12466626290612</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.486591168979318</v>
+        <v>7.527887168368795</v>
       </c>
       <c r="C21" t="n">
-        <v>84.22415065101733</v>
+        <v>87.51168833228724</v>
       </c>
       <c r="D21" t="n">
-        <v>6.550767272856904</v>
+        <v>7.527887168368795</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_9_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497611103198</v>
+        <v>10.84497645377612</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890711712021</v>
+        <v>37.78907236548621</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.663923489978101</v>
+        <v>4.704534998750716</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6941366846315</v>
+        <v>7.473063524726721</v>
       </c>
       <c r="D2" t="n">
-        <v>26.27942254727862</v>
+        <v>27.09034615098648</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.01984024272996</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="C3" t="n">
-        <v>25.69233742013903</v>
+        <v>35.56871932486194</v>
       </c>
       <c r="D3" t="n">
-        <v>57.87402716534947</v>
+        <v>88.22475744213962</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.58843639440489</v>
+        <v>36.84597308808704</v>
       </c>
       <c r="C4" t="n">
-        <v>82.74071476621694</v>
+        <v>57.49605429921445</v>
       </c>
       <c r="D4" t="n">
-        <v>67.39992513965628</v>
+        <v>122.6114525310884</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.38882281527331</v>
+        <v>44.35045253934967</v>
       </c>
       <c r="C5" t="n">
-        <v>114.7663066264522</v>
+        <v>96.33399347921829</v>
       </c>
       <c r="D5" t="n">
-        <v>48.37561812676159</v>
+        <v>89.41267216427826</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.03909964838319</v>
+        <v>38.64158963915446</v>
       </c>
       <c r="C6" t="n">
-        <v>82.55614619781855</v>
+        <v>110.5712986862055</v>
       </c>
       <c r="D6" t="n">
-        <v>38.80259626265094</v>
+        <v>54.78250364467628</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.72856427420492</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C7" t="n">
-        <v>62.34196096737671</v>
+        <v>105.4603201378966</v>
       </c>
       <c r="D7" t="n">
-        <v>37.84833749412304</v>
+        <v>41.26187426178919</v>
       </c>
     </row>
     <row r="8">
@@ -864,10 +864,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.86075605691297</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>41.14013754646259</v>
+        <v>68.76160920544659</v>
       </c>
       <c r="D8" t="n">
         <v>36.13322425480386</v>
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.096874227550941</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>39.60468413702056</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.27567548291088</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.733361820783536</v>
+        <v>7.671132672344868</v>
       </c>
       <c r="C21" t="n">
-        <v>96.66702275979421</v>
+        <v>93.01248365218152</v>
       </c>
       <c r="D21" t="n">
-        <v>8.700032048381479</v>
+        <v>7.671132672344868</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.552405162321465</v>
+        <v>6.324418710757953</v>
       </c>
       <c r="C2" t="n">
-        <v>7.387651474457248</v>
+        <v>6.303802008968769</v>
       </c>
       <c r="D2" t="n">
-        <v>23.00333045820701</v>
+        <v>29.17852351791945</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.05205799052086</v>
+        <v>16.23810702824224</v>
       </c>
       <c r="C3" t="n">
-        <v>23.67975462643307</v>
+        <v>32.05897128217959</v>
       </c>
       <c r="D3" t="n">
-        <v>64.47628047640927</v>
+        <v>88.71563129426302</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.3541996037174</v>
+        <v>34.22961545626929</v>
       </c>
       <c r="C4" t="n">
-        <v>73.05381016841365</v>
+        <v>72.19870791801469</v>
       </c>
       <c r="D4" t="n">
-        <v>79.7031873692773</v>
+        <v>136.3058512576272</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.01561981893928</v>
+        <v>49.55371537185777</v>
       </c>
       <c r="C5" t="n">
-        <v>132.5604837659256</v>
+        <v>100.8745766113598</v>
       </c>
       <c r="D5" t="n">
-        <v>59.69026041820608</v>
+        <v>108.3113154710294</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.55107322838128</v>
+        <v>48.02022545782425</v>
       </c>
       <c r="C6" t="n">
-        <v>131.3814047731252</v>
+        <v>129.3285703235451</v>
       </c>
       <c r="D6" t="n">
-        <v>44.88059629964295</v>
+        <v>68.14605339488386</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.92736033654828</v>
+        <v>34.7941203862112</v>
       </c>
       <c r="C7" t="n">
-        <v>89.53048188878788</v>
+        <v>131.4511088601267</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.95803119509142</v>
+        <v>19.77730750205199</v>
       </c>
       <c r="C8" t="n">
-        <v>61.66848204226339</v>
+        <v>100.9727513817844</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.42187377538564</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>40.15937158992001</v>
+        <v>60.90468232835936</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.16718451382499</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.117670855789377</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>37.86600895279948</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
         <v>35.79943003535993</v>
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.923120258822921</v>
+        <v>7.848449442569917</v>
       </c>
       <c r="C21" t="n">
-        <v>105.9717334617566</v>
+        <v>101.0487865730877</v>
       </c>
       <c r="D21" t="n">
-        <v>9.903900323528651</v>
+        <v>8.829505622891157</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.60680219668254</v>
+        <v>6.941938016729196</v>
       </c>
       <c r="C2" t="n">
-        <v>9.261807841864409</v>
+        <v>9.432631942403354</v>
       </c>
       <c r="D2" t="n">
-        <v>22.41526358336318</v>
+        <v>23.85745096090174</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.10881943091793</v>
+        <v>18.32432089976671</v>
       </c>
       <c r="C3" t="n">
-        <v>26.00158794697677</v>
+        <v>28.2694251437869</v>
       </c>
       <c r="D3" t="n">
-        <v>66.714665242092</v>
+        <v>89.89863727788043</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.4472857091716</v>
+        <v>31.97061398879738</v>
       </c>
       <c r="C4" t="n">
-        <v>66.23851760553229</v>
+        <v>74.81506554983244</v>
       </c>
       <c r="D4" t="n">
-        <v>90.01546525468579</v>
+        <v>144.435703996495</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.37810570598461</v>
+        <v>49.94641445355649</v>
       </c>
       <c r="C5" t="n">
-        <v>132.0205225285899</v>
+        <v>114.7908503190583</v>
       </c>
       <c r="D5" t="n">
-        <v>72.23208733995908</v>
+        <v>127.1608713925681</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.16492758544281</v>
+        <v>55.54728510628455</v>
       </c>
       <c r="C6" t="n">
-        <v>167.2858818128395</v>
+        <v>141.444318741655</v>
       </c>
       <c r="D6" t="n">
-        <v>51.4818678629985</v>
+        <v>81.26809320984674</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>60.30581622876881</v>
+        <v>43.95677170994669</v>
       </c>
       <c r="C7" t="n">
-        <v>133.2477071588984</v>
+        <v>154.567340304322</v>
       </c>
       <c r="D7" t="n">
-        <v>43.6573386601514</v>
+        <v>53.41885608347744</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>40.55599766243574</v>
+        <v>27.37112599440107</v>
       </c>
       <c r="C8" t="n">
-        <v>87.53753404916685</v>
+        <v>133.1004450032613</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>41.30703465618455</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.1890607007589</v>
+        <v>13.97812381306608</v>
       </c>
       <c r="C9" t="n">
-        <v>56.13437023342411</v>
+        <v>87.52968006753285</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>36.83124687252333</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>51.95899724726245</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.863979037466197</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>32.00006641992479</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>11.43245201595411</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.097023844787531</v>
+        <v>8.010339764094574</v>
       </c>
       <c r="C21" t="n">
-        <v>114.3704618076239</v>
+        <v>109.1408792857886</v>
       </c>
       <c r="D21" t="n">
-        <v>11.13340778658285</v>
+        <v>10.01292470511822</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.689849840916018</v>
+        <v>6.372524348266047</v>
       </c>
       <c r="C2" t="n">
-        <v>6.14966761940202</v>
+        <v>6.413757751844412</v>
       </c>
       <c r="D2" t="n">
-        <v>18.26443428980766</v>
+        <v>19.94813160259094</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>34.71950756068845</v>
+        <v>22.02550974477719</v>
       </c>
       <c r="C3" t="n">
-        <v>41.28249096357838</v>
+        <v>44.67442928175111</v>
       </c>
       <c r="D3" t="n">
-        <v>72.68369128391261</v>
+        <v>99.04852588146071</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.92407093607028</v>
+        <v>23.99391389179205</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4163214176548</v>
+        <v>98.23465703464009</v>
       </c>
       <c r="D4" t="n">
-        <v>85.21668247632739</v>
+        <v>139.9815146623272</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.07985002587604</v>
+        <v>31.29320807286709</v>
       </c>
       <c r="C5" t="n">
-        <v>99.94191629232532</v>
+        <v>84.50393364304422</v>
       </c>
       <c r="D5" t="n">
-        <v>50.85453107998479</v>
+        <v>82.73678777539996</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.43403996293088</v>
+        <v>27.29062268265284</v>
       </c>
       <c r="C6" t="n">
-        <v>87.74860980557993</v>
+        <v>101.7964377056475</v>
       </c>
       <c r="D6" t="n">
-        <v>28.73968229412113</v>
+        <v>35.17994723398021</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.88908787161589</v>
+        <v>18.1456428175938</v>
       </c>
       <c r="C7" t="n">
-        <v>61.56343503790898</v>
+        <v>93.60277136600364</v>
       </c>
       <c r="D7" t="n">
-        <v>28.02693346083794</v>
+        <v>29.04500583014188</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>41.30703465618455</v>
+        <v>64.50573290753667</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>30.39687241888974</v>
+        <v>39.60468413702056</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.04362317181014</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>26.03594911662541</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
         <v>17.9443845382232</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
-        <v>9.628981483252716</v>
+        <v>9.027170140549421</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.830599615521806</v>
+        <v>3.799363615435156</v>
       </c>
       <c r="C2" t="n">
-        <v>3.244676162535709</v>
+        <v>3.135702167364312</v>
       </c>
       <c r="D2" t="n">
-        <v>13.544191327789</v>
+        <v>14.55342796775472</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>35.21038141281186</v>
+        <v>22.58019719767664</v>
       </c>
       <c r="C3" t="n">
-        <v>32.84927818409827</v>
+        <v>35.38218726105504</v>
       </c>
       <c r="D3" t="n">
-        <v>71.7608484419206</v>
+        <v>94.38522428628835</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.91575929054657</v>
+        <v>31.91956310817654</v>
       </c>
       <c r="C4" t="n">
-        <v>106.122018090559</v>
+        <v>107.2706629045277</v>
       </c>
       <c r="D4" t="n">
-        <v>99.37053912845366</v>
+        <v>153.9949813927462</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.13585070274711</v>
+        <v>34.97476196379262</v>
       </c>
       <c r="C5" t="n">
-        <v>145.3968349989526</v>
+        <v>129.885221271853</v>
       </c>
       <c r="D5" t="n">
-        <v>65.9489020327795</v>
+        <v>105.0715480470149</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.36361617013237</v>
+        <v>32.60384125803657</v>
       </c>
       <c r="C6" t="n">
-        <v>120.8354709341059</v>
+        <v>120.7147159664836</v>
       </c>
       <c r="D6" t="n">
-        <v>34.45541742824607</v>
+        <v>45.40386782600649</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>85.93728529124455</v>
+        <v>116.1800233205675</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24273802932299</v>
+        <v>31.9794497181356</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.18348900970292</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>55.7436346471339</v>
+        <v>85.36787162278139</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>44.37499623195582</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
         <v>15.29268398905256</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
-        <v>8.025787482217675</v>
+        <v>7.490734983403163</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.942518853805943</v>
+        <v>4.671155576806324</v>
       </c>
       <c r="C2" t="n">
-        <v>11.76035574917254</v>
+        <v>8.02382398680918</v>
       </c>
       <c r="D2" t="n">
-        <v>17.36220814960484</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.36130851735861</v>
+        <v>17.88253443285565</v>
       </c>
       <c r="C3" t="n">
-        <v>21.82916020392783</v>
+        <v>23.16433708170349</v>
       </c>
       <c r="D3" t="n">
-        <v>66.23851760553229</v>
+        <v>85.09789100411354</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.52157973952487</v>
+        <v>37.088464771036</v>
       </c>
       <c r="C4" t="n">
-        <v>93.37206065550565</v>
+        <v>97.55823286641404</v>
       </c>
       <c r="D4" t="n">
-        <v>111.4185469549705</v>
+        <v>164.2306829572235</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.01499792413352</v>
+        <v>41.06159773012285</v>
       </c>
       <c r="C5" t="n">
-        <v>172.4930716361646</v>
+        <v>164.3691093835222</v>
       </c>
       <c r="D5" t="n">
-        <v>84.3566714874072</v>
+        <v>131.2105806725862</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.97117913034091</v>
+        <v>39.52712606838509</v>
       </c>
       <c r="C6" t="n">
-        <v>173.8066500644468</v>
+        <v>160.2820936907428</v>
       </c>
       <c r="D6" t="n">
-        <v>45.28311285838414</v>
+        <v>63.07434475474484</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.60879105428681</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>128.9957578518054</v>
+        <v>144.5662764411598</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.10833640483241</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C8" t="n">
-        <v>83.19820919639595</v>
+        <v>116.9114253602314</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47499562906875</v>
+        <v>70.44530651822986</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>37.43894870145212</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.11769621798515</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>29.50740899884213</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.29272504678157</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>17.20021977840412</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>6.955682484588652</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.534291735288517</v>
+        <v>2.752820562708056</v>
       </c>
       <c r="C2" t="n">
-        <v>5.300455855228529</v>
+        <v>3.78267390446296</v>
       </c>
       <c r="D2" t="n">
-        <v>11.97732199181109</v>
+        <v>16.73879835740811</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.94406574305371</v>
+        <v>18.67284133477433</v>
       </c>
       <c r="C3" t="n">
-        <v>34.10591524553419</v>
+        <v>28.15652415779852</v>
       </c>
       <c r="D3" t="n">
-        <v>66.95028469111124</v>
+        <v>86.81104074802421</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>63.30309196983433</v>
+        <v>40.68755185480481</v>
       </c>
       <c r="C4" t="n">
-        <v>87.73093834690347</v>
+        <v>92.70839920743479</v>
       </c>
       <c r="D4" t="n">
-        <v>119.2038062496477</v>
+        <v>172.6923664201267</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.07666810305183</v>
+        <v>42.80419990516094</v>
       </c>
       <c r="C5" t="n">
-        <v>199.5156771955581</v>
+        <v>195.2696183746906</v>
       </c>
       <c r="D5" t="n">
-        <v>91.91612881010764</v>
+        <v>137.9355524466769</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.36361617013237</v>
+        <v>31.87931145230244</v>
       </c>
       <c r="C6" t="n">
-        <v>208.8658423308047</v>
+        <v>192.0003985195488</v>
       </c>
       <c r="D6" t="n">
-        <v>45.12210623488766</v>
+        <v>61.02151030516475</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.97732199181109</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>126.420633623566</v>
+        <v>151.6328964163284</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>36.11162580531042</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>64.83952712698058</v>
+        <v>87.37063693944488</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.66664774891259</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.828235209485814</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="C2" t="n">
-        <v>6.563965150594174</v>
+        <v>8.632507563442203</v>
       </c>
       <c r="D2" t="n">
-        <v>14.28835608760808</v>
+        <v>22.52816456935156</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.70858516275472</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="C3" t="n">
-        <v>27.06678420608456</v>
+        <v>21.34810382884689</v>
       </c>
       <c r="D3" t="n">
-        <v>61.48685871697774</v>
+        <v>81.38197594353935</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.84064774340508</v>
+        <v>38.65827935012666</v>
       </c>
       <c r="C4" t="n">
-        <v>87.20766682053993</v>
+        <v>82.48546036311276</v>
       </c>
       <c r="D4" t="n">
-        <v>124.5258605543697</v>
+        <v>175.5767411752038</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.93189352663781</v>
+        <v>50.60909415392309</v>
       </c>
       <c r="C5" t="n">
-        <v>183.071403149424</v>
+        <v>185.5748597952534</v>
       </c>
       <c r="D5" t="n">
-        <v>110.2011798017045</v>
+        <v>161.6938468894497</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.69320566131882</v>
+        <v>41.57996051796516</v>
       </c>
       <c r="C6" t="n">
-        <v>260.0659486026844</v>
+        <v>245.0520809616379</v>
       </c>
       <c r="D6" t="n">
-        <v>60.17622553180826</v>
+        <v>82.39513957432206</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.05067533218911</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="C7" t="n">
-        <v>204.6924328400515</v>
+        <v>205.5907319894373</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.593818492349078</v>
+        <v>5.17381040138069</v>
       </c>
       <c r="C8" t="n">
-        <v>107.4817386609408</v>
+        <v>134.7694161004809</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>48.47968338341173</v>
+        <v>58.3531200450219</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.632466505713198</v>
+        <v>1.823105486786327</v>
       </c>
       <c r="C2" t="n">
-        <v>4.557272843113694</v>
+        <v>5.262167694762903</v>
       </c>
       <c r="D2" t="n">
-        <v>10.52433538952581</v>
+        <v>16.44427404613407</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.53539665617978</v>
+        <v>12.21294144083032</v>
       </c>
       <c r="C3" t="n">
-        <v>26.8851608807989</v>
+        <v>27.07660168312703</v>
       </c>
       <c r="D3" t="n">
-        <v>59.33192250615598</v>
+        <v>80.70457002760905</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.47205038595602</v>
+        <v>35.1357685872891</v>
       </c>
       <c r="C4" t="n">
-        <v>80.11159441424397</v>
+        <v>72.26252151879073</v>
       </c>
       <c r="D4" t="n">
-        <v>126.6827602605999</v>
+        <v>178.4483532101258</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>81.33779729684825</v>
+        <v>55.07604620824608</v>
       </c>
       <c r="C5" t="n">
-        <v>180.5188591183823</v>
+        <v>179.2671307954676</v>
       </c>
       <c r="D5" t="n">
-        <v>123.8474728907351</v>
+        <v>176.9109363052752</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>71.60769580005812</v>
+        <v>48.46299367243955</v>
       </c>
       <c r="C6" t="n">
-        <v>283.6936706007924</v>
+        <v>273.0672334500249</v>
       </c>
       <c r="D6" t="n">
-        <v>71.04417261782045</v>
+        <v>99.58259663257098</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.49362347325367</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>265.0581356787793</v>
+        <v>254.937298595699</v>
       </c>
       <c r="D7" t="n">
-        <v>41.86074036137975</v>
+        <v>48.44826745687584</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.175193059712437</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>147.9542877685155</v>
+        <v>173.823339775419</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>58.79687000734145</v>
+        <v>66.45155685735384</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>7.525096153051802</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.738315331322607</v>
+        <v>2.734167356327367</v>
       </c>
       <c r="C2" t="n">
-        <v>12.06077054667207</v>
+        <v>10.36332876602933</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13832861530756</v>
+        <v>15.30053797068654</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.4821612959722</v>
+        <v>9.385508052599507</v>
       </c>
       <c r="C3" t="n">
-        <v>22.39366513386975</v>
+        <v>23.81719930502762</v>
       </c>
       <c r="D3" t="n">
-        <v>54.72752577323844</v>
+        <v>75.71729169003525</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.72507925174444</v>
+        <v>29.52017171899734</v>
       </c>
       <c r="C4" t="n">
-        <v>74.0237769002095</v>
+        <v>69.96523189085319</v>
       </c>
       <c r="D4" t="n">
-        <v>126.7976247419968</v>
+        <v>177.542200079106</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79.76700097005336</v>
+        <v>54.09429850399926</v>
       </c>
       <c r="C5" t="n">
-        <v>165.8417309398925</v>
+        <v>159.288565014045</v>
       </c>
       <c r="D5" t="n">
-        <v>134.9903093339364</v>
+        <v>193.8706278961389</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>86.38005350585986</v>
+        <v>58.08313942635406</v>
       </c>
       <c r="C6" t="n">
-        <v>286.1087699532395</v>
+        <v>278.7829685841498</v>
       </c>
       <c r="D6" t="n">
-        <v>87.86936477320229</v>
+        <v>122.0832722662036</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.27427712904591</v>
+        <v>29.64387192973244</v>
       </c>
       <c r="C7" t="n">
-        <v>324.9447456378347</v>
+        <v>313.6860629655323</v>
       </c>
       <c r="D7" t="n">
-        <v>49.52622643613884</v>
+        <v>59.6470635192192</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>229.5669744225529</v>
+        <v>235.9090645919873</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.217187226816797</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>105.2796785603152</v>
+        <v>120.2562397886003</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>47.54604131667303</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>7.166758241001715</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.355253800217104</v>
+        <v>4.516039439535327</v>
       </c>
       <c r="C2" t="n">
-        <v>2.952115346670159</v>
+        <v>5.998478472948011</v>
       </c>
       <c r="D2" t="n">
-        <v>6.039711876526377</v>
+        <v>12.54477216486574</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.108614142272901</v>
+        <v>1.97920337176157</v>
       </c>
       <c r="C2" t="n">
-        <v>6.849653732529996</v>
+        <v>5.969026041820607</v>
       </c>
       <c r="D2" t="n">
-        <v>8.932922360941728</v>
+        <v>11.38336463074177</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.01430960940298</v>
+        <v>12.76272015520853</v>
       </c>
       <c r="C3" t="n">
-        <v>33.11925880276615</v>
+        <v>32.18168974521045</v>
       </c>
       <c r="D3" t="n">
-        <v>59.69516915672731</v>
+        <v>81.55869053030378</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>60.63568345739575</v>
+        <v>41.05767073930586</v>
       </c>
       <c r="C4" t="n">
-        <v>103.6971012610693</v>
+        <v>99.34501368814324</v>
       </c>
       <c r="D4" t="n">
-        <v>129.3756942133489</v>
+        <v>182.6983390218102</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.85453107998479</v>
+        <v>33.72303364087794</v>
       </c>
       <c r="C5" t="n">
-        <v>245.0196832873978</v>
+        <v>237.3865948868788</v>
       </c>
       <c r="D5" t="n">
-        <v>124.7310458245573</v>
+        <v>176.0519070640593</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.09565580013523</v>
+        <v>18.39500673447249</v>
       </c>
       <c r="C6" t="n">
-        <v>270.0886109153401</v>
+        <v>258.4961340235937</v>
       </c>
       <c r="D6" t="n">
-        <v>71.40643752068752</v>
+        <v>93.98761646606842</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>161.3944138396544</v>
+        <v>165.8859095865836</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.169662426385451</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>77.60715602071035</v>
+        <v>88.62236526235957</v>
       </c>
       <c r="D8" t="n">
-        <v>25.2849121228766</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>36.27655941962388</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.06125357275758</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.23654444346124</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.838453597155781</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.055239913345078</v>
+        <v>6.280240064066846</v>
       </c>
       <c r="C2" t="n">
-        <v>1.941896959000191</v>
+        <v>7.791149780902686</v>
       </c>
       <c r="D2" t="n">
-        <v>6.310674242898497</v>
+        <v>31.01831871567797</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.61960597456675</v>
+        <v>9.601492547533805</v>
       </c>
       <c r="C3" t="n">
-        <v>7.554548584179206</v>
+        <v>15.11400590687965</v>
       </c>
       <c r="D3" t="n">
-        <v>8.452847733565036</v>
+        <v>13.67574552015807</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4574,7 +4574,7 @@
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39919723595008</v>
+        <v>13.39804324627068</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14873847056219</v>
+        <v>70.14269699518178</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576376145405892</v>
+        <v>1.576240381914197</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.910702016642545</v>
+        <v>4.587707021945345</v>
       </c>
       <c r="C2" t="n">
-        <v>5.070726892434775</v>
+        <v>3.794454876913922</v>
       </c>
       <c r="D2" t="n">
-        <v>9.208793465835081</v>
+        <v>23.73178725475815</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.27232932917064</v>
+        <v>16.81733817374786</v>
       </c>
       <c r="C3" t="n">
-        <v>7.569274799742908</v>
+        <v>24.66641106920111</v>
       </c>
       <c r="D3" t="n">
-        <v>11.70734137314322</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.07201173977529</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C4" t="n">
-        <v>12.23944862884498</v>
+        <v>23.59826956698058</v>
       </c>
       <c r="D4" t="n">
-        <v>19.50143639715864</v>
+        <v>22.23265851037327</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.84843530511426</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>26.87534340375643</v>
+        <v>26.51700549170635</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44646262624982</v>
+        <v>15.43840995984147</v>
       </c>
       <c r="C21" t="n">
-        <v>86.17500202013056</v>
+        <v>86.13007661806292</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251886868684172</v>
+        <v>3.25019157049294</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.419247327442394</v>
+        <v>4.87535909928966</v>
       </c>
       <c r="C2" t="n">
-        <v>3.908337610606552</v>
+        <v>7.710646469154449</v>
       </c>
       <c r="D2" t="n">
-        <v>11.96455927165588</v>
+        <v>33.97436105316512</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.73312885536089</v>
+        <v>16.29701189049705</v>
       </c>
       <c r="C3" t="n">
-        <v>15.07473599870977</v>
+        <v>18.66302385773187</v>
       </c>
       <c r="D3" t="n">
-        <v>16.35591675275186</v>
+        <v>46.95699269412494</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.78292025083699</v>
+        <v>23.34301516387641</v>
       </c>
       <c r="C4" t="n">
-        <v>16.25970547773567</v>
+        <v>46.0606570401476</v>
       </c>
       <c r="D4" t="n">
-        <v>20.81599657314512</v>
+        <v>35.46759931132452</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.70796326794897</v>
+        <v>10.18563243156066</v>
       </c>
       <c r="C5" t="n">
-        <v>15.36435157146258</v>
+        <v>27.19441140763665</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>30.65507206510666</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.13430381349934</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.51451791248334</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>40.82499653339935</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.82369599052563</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,7 +5260,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
         <v>31.27455486648638</v>
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.95035713990669</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5361,10 +5361,10 @@
         <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74887760281566</v>
+        <v>16.72956338642046</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1681533771755</v>
+        <v>102.0503366571648</v>
       </c>
       <c r="D21" t="n">
-        <v>5.024663280844698</v>
+        <v>4.182390846605114</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.615016031215008</v>
+        <v>6.33718143091316</v>
       </c>
       <c r="C2" t="n">
-        <v>7.358199043329844</v>
+        <v>4.202861921880595</v>
       </c>
       <c r="D2" t="n">
-        <v>23.20458873757761</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.1440802328128</v>
+        <v>16.46390900021901</v>
       </c>
       <c r="C3" t="n">
-        <v>15.28581175512284</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="D3" t="n">
-        <v>22.28567288640259</v>
+        <v>62.33116174262999</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.51414236405162</v>
+        <v>27.54195009494002</v>
       </c>
       <c r="C4" t="n">
-        <v>28.30771330425253</v>
+        <v>46.41801320449344</v>
       </c>
       <c r="D4" t="n">
-        <v>23.94286301117121</v>
+        <v>50.18301565027996</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.4285093296039</v>
+        <v>22.55565350507047</v>
       </c>
       <c r="C5" t="n">
-        <v>23.58648859452962</v>
+        <v>58.4385320952914</v>
       </c>
       <c r="D5" t="n">
-        <v>30.75324683553134</v>
+        <v>35.9074222828271</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.8063179648229</v>
+        <v>9.821404033285093</v>
       </c>
       <c r="C6" t="n">
-        <v>18.79752329321368</v>
+        <v>28.13590745600934</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>38.40007970390975</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84054026575129</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>39.97185777840888</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.56104526967722</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>46.09305471438775</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.91411459030757</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.08992283736101</v>
+        <v>18.0504668646636</v>
       </c>
       <c r="C21" t="n">
-        <v>118.0152108913551</v>
+        <v>117.7578076409006</v>
       </c>
       <c r="D21" t="n">
-        <v>6.891399176137526</v>
+        <v>6.016822288221199</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.444592841303563</v>
+        <v>6.663121668723102</v>
       </c>
       <c r="C2" t="n">
-        <v>13.46957850226624</v>
+        <v>8.331111018238433</v>
       </c>
       <c r="D2" t="n">
-        <v>24.5780537758189</v>
+        <v>39.79907018246145</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.06063167795183</v>
+        <v>17.28857707178633</v>
       </c>
       <c r="C3" t="n">
-        <v>21.84388641949153</v>
+        <v>19.08517537055799</v>
       </c>
       <c r="D3" t="n">
-        <v>33.61013265488955</v>
+        <v>67.49515466696822</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.10801760966293</v>
+        <v>21.8242514654066</v>
       </c>
       <c r="C4" t="n">
-        <v>28.60125586782233</v>
+        <v>46.03513159983719</v>
       </c>
       <c r="D4" t="n">
-        <v>25.95937279569416</v>
+        <v>60.27832729304991</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.3171298706675</v>
+        <v>19.43860454408685</v>
       </c>
       <c r="C5" t="n">
-        <v>29.28062527916113</v>
+        <v>54.29064804484862</v>
       </c>
       <c r="D5" t="n">
-        <v>26.43355693684537</v>
+        <v>36.3982961349505</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.54343056426301</v>
+        <v>10.94845039776043</v>
       </c>
       <c r="C6" t="n">
-        <v>19.68305972244431</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="D6" t="n">
-        <v>30.14849024971531</v>
+        <v>31.87931145230244</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>15.69029180927252</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6000,7 +6000,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.07695771014859</v>
+        <v>7.052949032062857</v>
       </c>
       <c r="C21" t="n">
-        <v>67.23109824641159</v>
+        <v>66.12139717558929</v>
       </c>
       <c r="D21" t="n">
-        <v>5.307718282611442</v>
+        <v>4.408093145039286</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.620325680363742</v>
+        <v>5.32794479094744</v>
       </c>
       <c r="C2" t="n">
-        <v>6.908558594784804</v>
+        <v>4.701589755637975</v>
       </c>
       <c r="D2" t="n">
-        <v>21.93911594680347</v>
+        <v>29.32676742126072</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.6846633649543</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="C3" t="n">
-        <v>42.89746593706438</v>
+        <v>27.76873381462103</v>
       </c>
       <c r="D3" t="n">
-        <v>46.79500432292422</v>
+        <v>84.6168346290326</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.07646281440679</v>
+        <v>29.20110371511713</v>
       </c>
       <c r="C4" t="n">
-        <v>45.32041927114551</v>
+        <v>47.23482729442679</v>
       </c>
       <c r="D4" t="n">
-        <v>38.1350078237631</v>
+        <v>81.08156114603983</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.9074222828271</v>
+        <v>27.02260555939346</v>
       </c>
       <c r="C5" t="n">
-        <v>44.47317100238052</v>
+        <v>73.18929135159972</v>
       </c>
       <c r="D5" t="n">
-        <v>30.09056713516474</v>
+        <v>51.32086123950202</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.73968229412113</v>
+        <v>19.76356303419254</v>
       </c>
       <c r="C6" t="n">
-        <v>36.26674194258143</v>
+        <v>67.78378849201678</v>
       </c>
       <c r="D6" t="n">
-        <v>32.36233132279187</v>
+        <v>36.74976181307086</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.3727863901733</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>23.65521093382689</v>
+        <v>43.05847256056086</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>20.27799883121787</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6213,7 +6213,7 @@
         <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.5935407549086</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.308312027015857</v>
+        <v>7.272112947759084</v>
       </c>
       <c r="C21" t="n">
-        <v>77.65081528704347</v>
+        <v>75.44817183300052</v>
       </c>
       <c r="D21" t="n">
-        <v>6.394773023638875</v>
+        <v>5.454084710819314</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.200137662946108</v>
+        <v>4.291219215262808</v>
       </c>
       <c r="C2" t="n">
-        <v>5.311255079975244</v>
+        <v>11.94983305609217</v>
       </c>
       <c r="D2" t="n">
-        <v>20.98878416909256</v>
+        <v>25.8386178280718</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.43217427851362</v>
+        <v>19.71349390127595</v>
       </c>
       <c r="C3" t="n">
-        <v>32.91309178487432</v>
+        <v>22.0991408225957</v>
       </c>
       <c r="D3" t="n">
-        <v>53.91758391723482</v>
+        <v>88.44565067559515</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.555416825359</v>
+        <v>35.42931115085889</v>
       </c>
       <c r="C4" t="n">
-        <v>83.1491218111836</v>
+        <v>60.15070009149782</v>
       </c>
       <c r="D4" t="n">
-        <v>53.80762817435918</v>
+        <v>105.2796785603152</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.59588946541137</v>
+        <v>36.20194659410114</v>
       </c>
       <c r="C5" t="n">
-        <v>67.27426143351269</v>
+        <v>80.42968067041996</v>
       </c>
       <c r="D5" t="n">
-        <v>37.47821860962199</v>
+        <v>68.32964021557801</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.45291415348983</v>
+        <v>28.61892732649877</v>
       </c>
       <c r="C6" t="n">
-        <v>56.23156325614456</v>
+        <v>94.59139130418019</v>
       </c>
       <c r="D6" t="n">
-        <v>34.65667570761666</v>
+        <v>44.88059629964295</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.45180923259856</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>40.24380189248525</v>
+        <v>73.00177754008857</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>26.95388322009618</v>
+        <v>41.47393176590651</v>
       </c>
       <c r="D8" t="n">
         <v>33.79666471869644</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>25.18281036163492</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.61656292046278</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.12466626290612</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.527887168368795</v>
+        <v>7.478776501289023</v>
       </c>
       <c r="C21" t="n">
-        <v>87.51168833228724</v>
+        <v>84.13623563950151</v>
       </c>
       <c r="D21" t="n">
-        <v>7.527887168368795</v>
+        <v>6.543929438627894</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_9_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_9_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497645377612</v>
+        <v>10.84497635880473</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907236548621</v>
+        <v>37.78907203456061</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.704534998750716</v>
+        <v>0.8217228284545803</v>
       </c>
       <c r="C2" t="n">
-        <v>7.473063524726721</v>
+        <v>3.339905689847649</v>
       </c>
       <c r="D2" t="n">
-        <v>27.09034615098648</v>
+        <v>9.707521299592461</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95969159086365</v>
+        <v>8.256498192715675</v>
       </c>
       <c r="C3" t="n">
-        <v>35.56871932486194</v>
+        <v>33.0259927708627</v>
       </c>
       <c r="D3" t="n">
-        <v>88.22475744213962</v>
+        <v>50.02495426989623</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.84597308808704</v>
+        <v>14.37082289476481</v>
       </c>
       <c r="C4" t="n">
-        <v>57.49605429921445</v>
+        <v>105.1648140789183</v>
       </c>
       <c r="D4" t="n">
-        <v>122.6114525310884</v>
+        <v>66.82560273267188</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.35045253934967</v>
+        <v>12.24730261047896</v>
       </c>
       <c r="C5" t="n">
-        <v>96.33399347921829</v>
+        <v>152.8335738586222</v>
       </c>
       <c r="D5" t="n">
-        <v>89.41267216427826</v>
+        <v>45.62672455487052</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.64158963915446</v>
+        <v>9.016370915802709</v>
       </c>
       <c r="C6" t="n">
-        <v>110.5712986862055</v>
+        <v>115.3612457352257</v>
       </c>
       <c r="D6" t="n">
-        <v>54.78250364467628</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>105.4603201378966</v>
+        <v>58.38944471007905</v>
       </c>
       <c r="D7" t="n">
-        <v>41.26187426178919</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>68.76160920544659</v>
+        <v>30.95941385342316</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.671132672344868</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.01248365218152</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.671132672344868</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.324418710757953</v>
+        <v>1.336158625479909</v>
       </c>
       <c r="C2" t="n">
-        <v>6.303802008968769</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D2" t="n">
-        <v>29.17852351791945</v>
+        <v>11.79471691882118</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.23810702824224</v>
+        <v>5.340707511102649</v>
       </c>
       <c r="C3" t="n">
-        <v>32.05897128217959</v>
+        <v>21.56408832378119</v>
       </c>
       <c r="D3" t="n">
-        <v>88.71563129426302</v>
+        <v>46.2746780396734</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.22961545626929</v>
+        <v>15.39184050718149</v>
       </c>
       <c r="C4" t="n">
-        <v>72.19870791801469</v>
+        <v>92.59353472603793</v>
       </c>
       <c r="D4" t="n">
-        <v>136.3058512576272</v>
+        <v>76.32106652814704</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.55371537185777</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C5" t="n">
-        <v>100.8745766113598</v>
+        <v>176.7145867644259</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3113154710294</v>
+        <v>58.56125055832225</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.02022545782425</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C6" t="n">
-        <v>129.3285703235451</v>
+        <v>181.4947163364036</v>
       </c>
       <c r="D6" t="n">
-        <v>68.14605339488386</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.7941203862112</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>131.4511088601267</v>
+        <v>112.1676204533108</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.77730750205199</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>100.9727513817844</v>
+        <v>53.40707511102648</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90468232835936</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>37.86600895279948</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>38.38240824523329</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.94316611080748</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.848449442569917</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0487865730877</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.829505622891157</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.941938016729196</v>
+        <v>0.719621067212912</v>
       </c>
       <c r="C2" t="n">
-        <v>9.432631942403354</v>
+        <v>6.015168183920207</v>
       </c>
       <c r="D2" t="n">
-        <v>23.85745096090174</v>
+        <v>8.095491569219199</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.32432089976671</v>
+        <v>5.492878405260904</v>
       </c>
       <c r="C3" t="n">
-        <v>28.2694251437869</v>
+        <v>38.99501881268331</v>
       </c>
       <c r="D3" t="n">
-        <v>89.89863727788043</v>
+        <v>46.61338099763856</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.97061398879738</v>
+        <v>16.54048532115026</v>
       </c>
       <c r="C4" t="n">
-        <v>74.81506554983244</v>
+        <v>86.416378170917</v>
       </c>
       <c r="D4" t="n">
-        <v>144.435703996495</v>
+        <v>82.30678228093984</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.94641445355649</v>
+        <v>16.86151682043897</v>
       </c>
       <c r="C5" t="n">
-        <v>114.7908503190583</v>
+        <v>199.9083762772568</v>
       </c>
       <c r="D5" t="n">
-        <v>127.1608713925681</v>
+        <v>65.23713494720056</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.54728510628455</v>
+        <v>10.54593383901924</v>
       </c>
       <c r="C6" t="n">
-        <v>141.444318741655</v>
+        <v>224.5639881217112</v>
       </c>
       <c r="D6" t="n">
-        <v>81.26809320984674</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.95677170994669</v>
+        <v>4.19206269713388</v>
       </c>
       <c r="C7" t="n">
-        <v>154.567340304322</v>
+        <v>103.5439486192068</v>
       </c>
       <c r="D7" t="n">
-        <v>53.41885608347744</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.37112599440107</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>133.1004450032613</v>
+        <v>44.56152829576272</v>
       </c>
       <c r="D8" t="n">
-        <v>41.30703465618455</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.97812381306608</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>87.52968006753285</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>51.95899724726245</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.010339764094574</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1408792857886</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01292470511822</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.372524348266047</v>
+        <v>1.148644813968768</v>
       </c>
       <c r="C2" t="n">
-        <v>6.413757751844412</v>
+        <v>12.36216709187584</v>
       </c>
       <c r="D2" t="n">
-        <v>19.94813160259094</v>
+        <v>7.853981633974483</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.02550974477719</v>
+        <v>3.96135198663588</v>
       </c>
       <c r="C3" t="n">
-        <v>44.67442928175111</v>
+        <v>30.44890504721482</v>
       </c>
       <c r="D3" t="n">
-        <v>99.04852588146071</v>
+        <v>42.51949307092936</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.99391389179205</v>
+        <v>13.82202592809084</v>
       </c>
       <c r="C4" t="n">
-        <v>98.23465703464009</v>
+        <v>93.20614529348792</v>
       </c>
       <c r="D4" t="n">
-        <v>139.9815146623272</v>
+        <v>86.51847993215866</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.29320807286709</v>
+        <v>20.69033286700153</v>
       </c>
       <c r="C5" t="n">
-        <v>84.50393364304422</v>
+        <v>181.1569951261427</v>
       </c>
       <c r="D5" t="n">
-        <v>82.73678777539996</v>
+        <v>78.417097876714</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.29062268265284</v>
+        <v>15.73839744678062</v>
       </c>
       <c r="C6" t="n">
-        <v>101.7964377056475</v>
+        <v>274.2747831262485</v>
       </c>
       <c r="D6" t="n">
-        <v>35.17994723398021</v>
+        <v>47.97997380195012</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>93.60277136600364</v>
+        <v>204.9319792798877</v>
       </c>
       <c r="D7" t="n">
-        <v>29.04500583014188</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>64.50573290753667</v>
+        <v>84.44993751931062</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>38.38437174064178</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.27455486648638</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.799363615435156</v>
+        <v>0.6400995031689203</v>
       </c>
       <c r="C2" t="n">
-        <v>3.135702167364312</v>
+        <v>6.006332454581986</v>
       </c>
       <c r="D2" t="n">
-        <v>14.55342796775472</v>
+        <v>6.135923151542564</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.58019719767664</v>
+        <v>4.015348110369454</v>
       </c>
       <c r="C3" t="n">
-        <v>35.38218726105504</v>
+        <v>39.72151211382595</v>
       </c>
       <c r="D3" t="n">
-        <v>94.38522428628835</v>
+        <v>39.72151211382595</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.91956310817654</v>
+        <v>11.69065166217102</v>
       </c>
       <c r="C4" t="n">
-        <v>107.2706629045277</v>
+        <v>87.61607386550659</v>
       </c>
       <c r="D4" t="n">
-        <v>153.9949813927462</v>
+        <v>88.17763355233576</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.97476196379262</v>
+        <v>21.94206118991621</v>
       </c>
       <c r="C5" t="n">
-        <v>129.885221271853</v>
+        <v>183.5622770015474</v>
       </c>
       <c r="D5" t="n">
-        <v>105.0715480470149</v>
+        <v>88.50455553784997</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.60384125803657</v>
+        <v>19.20003985195487</v>
       </c>
       <c r="C6" t="n">
-        <v>120.7147159664836</v>
+        <v>296.1716839217693</v>
       </c>
       <c r="D6" t="n">
-        <v>45.40386782600649</v>
+        <v>56.07055663264809</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>116.1800233205675</v>
+        <v>274.6399932722282</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>85.36787162278139</v>
+        <v>129.8459513636831</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>39.38771789438203</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>49.81093327037041</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.74128593663113</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.671155576806324</v>
+        <v>0.9768389657255763</v>
       </c>
       <c r="C2" t="n">
-        <v>8.02382398680918</v>
+        <v>15.24556009924872</v>
       </c>
       <c r="D2" t="n">
-        <v>23.98900515327081</v>
+        <v>8.281041885321844</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.88253443285565</v>
+        <v>3.107231483941155</v>
       </c>
       <c r="C3" t="n">
-        <v>23.16433708170349</v>
+        <v>31.59754986118359</v>
       </c>
       <c r="D3" t="n">
-        <v>85.09789100411354</v>
+        <v>36.20194659410114</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.088464771036</v>
+        <v>9.737955478424112</v>
       </c>
       <c r="C4" t="n">
-        <v>97.55823286641404</v>
+        <v>93.0019417710046</v>
       </c>
       <c r="D4" t="n">
-        <v>164.2306829572235</v>
+        <v>87.80751466783472</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.06159773012285</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C5" t="n">
-        <v>164.3691093835222</v>
+        <v>173.0821202587127</v>
       </c>
       <c r="D5" t="n">
-        <v>131.2105806725862</v>
+        <v>96.62851779049234</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.52712606838509</v>
+        <v>23.50696703048563</v>
       </c>
       <c r="C6" t="n">
-        <v>160.2820936907428</v>
+        <v>298.3855249948459</v>
       </c>
       <c r="D6" t="n">
-        <v>63.07434475474484</v>
+        <v>68.14605339488386</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>13.41460063082842</v>
       </c>
       <c r="C7" t="n">
-        <v>144.5662764411598</v>
+        <v>341.1740169367388</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>45.51382356888213</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.10004045484194</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>116.9114253602314</v>
+        <v>227.6476576607504</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>70.44530651822986</v>
+        <v>93.52030455884689</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.752820562708056</v>
+        <v>0.6715154297048183</v>
       </c>
       <c r="C2" t="n">
-        <v>3.78267390446296</v>
+        <v>8.293804605477055</v>
       </c>
       <c r="D2" t="n">
-        <v>16.73879835740811</v>
+        <v>6.027930904075415</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.67284133477433</v>
+        <v>4.309872421643497</v>
       </c>
       <c r="C3" t="n">
-        <v>28.15652415779852</v>
+        <v>45.59727212374311</v>
       </c>
       <c r="D3" t="n">
-        <v>86.81104074802421</v>
+        <v>39.67733346713484</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.68755185480481</v>
+        <v>14.71541633895544</v>
       </c>
       <c r="C4" t="n">
-        <v>92.70839920743479</v>
+        <v>125.3682000846134</v>
       </c>
       <c r="D4" t="n">
-        <v>172.6923664201267</v>
+        <v>90.80675390430872</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.80419990516094</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C5" t="n">
-        <v>195.2696183746906</v>
+        <v>255.2544031041707</v>
       </c>
       <c r="D5" t="n">
-        <v>137.9355524466769</v>
+        <v>90.44350725373742</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.87931145230244</v>
+        <v>8.291841110068562</v>
       </c>
       <c r="C6" t="n">
-        <v>192.0003985195488</v>
+        <v>291.9452600549868</v>
       </c>
       <c r="D6" t="n">
-        <v>61.02151030516475</v>
+        <v>59.81396062894117</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.964919124554372</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>151.6328964163284</v>
+        <v>160.0769084205552</v>
       </c>
       <c r="D7" t="n">
-        <v>36.11162580531042</v>
+        <v>35.33309987584271</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>87.37063693944488</v>
+        <v>68.92850631516855</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.18124777685393</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.670353755551324</v>
+        <v>0.3583379120500858</v>
       </c>
       <c r="C2" t="n">
-        <v>8.632507563442203</v>
+        <v>4.069344234103029</v>
       </c>
       <c r="D2" t="n">
-        <v>22.52816456935156</v>
+        <v>4.528802159690536</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.21570675749381</v>
+        <v>3.303581024790517</v>
       </c>
       <c r="C3" t="n">
-        <v>21.34810382884689</v>
+        <v>38.56304982281472</v>
       </c>
       <c r="D3" t="n">
-        <v>81.38197594353935</v>
+        <v>35.59326301746811</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.65827935012666</v>
+        <v>10.78449853115121</v>
       </c>
       <c r="C4" t="n">
-        <v>82.48546036311276</v>
+        <v>115.6430073263445</v>
       </c>
       <c r="D4" t="n">
-        <v>175.5767411752038</v>
+        <v>86.35256457014096</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.60909415392309</v>
+        <v>13.91627370769854</v>
       </c>
       <c r="C5" t="n">
-        <v>185.5748597952534</v>
+        <v>218.1197961910351</v>
       </c>
       <c r="D5" t="n">
-        <v>161.6938468894497</v>
+        <v>90.68894417979912</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.57996051796516</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>245.0520809616379</v>
+        <v>285.1024785563865</v>
       </c>
       <c r="D6" t="n">
-        <v>82.39513957432206</v>
+        <v>61.102013616913</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.6066633279623</v>
+        <v>2.994330497952772</v>
       </c>
       <c r="C7" t="n">
-        <v>205.5907319894373</v>
+        <v>196.667627105538</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>134.7694161004809</v>
+        <v>80.36095833112266</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>26.70353755551324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>58.3531200450219</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>17.36711688812608</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>13.14952875068177</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.823105486786327</v>
+        <v>0.4427682146153115</v>
       </c>
       <c r="C2" t="n">
-        <v>5.262167694762903</v>
+        <v>5.695118432335748</v>
       </c>
       <c r="D2" t="n">
-        <v>16.44427404613407</v>
+        <v>6.517823008494575</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.21294144083032</v>
+        <v>2.189297380470387</v>
       </c>
       <c r="C3" t="n">
-        <v>27.07660168312703</v>
+        <v>25.40272184738622</v>
       </c>
       <c r="D3" t="n">
-        <v>80.70457002760905</v>
+        <v>31.11649348610266</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.1357685872891</v>
+        <v>8.602073384610552</v>
       </c>
       <c r="C4" t="n">
-        <v>72.26252151879073</v>
+        <v>104.960610556435</v>
       </c>
       <c r="D4" t="n">
-        <v>178.4483532101258</v>
+        <v>84.84656359182634</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.07604620824608</v>
+        <v>15.16800203061322</v>
       </c>
       <c r="C5" t="n">
-        <v>179.2671307954676</v>
+        <v>217.8743592649734</v>
       </c>
       <c r="D5" t="n">
-        <v>176.9109363052752</v>
+        <v>100.9482076891783</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.46299367243955</v>
+        <v>13.24279478258523</v>
       </c>
       <c r="C6" t="n">
-        <v>273.0672334500249</v>
+        <v>317.6258165026749</v>
       </c>
       <c r="D6" t="n">
-        <v>99.58259663257098</v>
+        <v>74.54606667886881</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>254.937298595699</v>
+        <v>307.7572885795859</v>
       </c>
       <c r="D7" t="n">
-        <v>48.44826745687584</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>173.823339775419</v>
+        <v>168.3991837094554</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>66.45155685735384</v>
+        <v>63.45624461169682</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>22.2984356065578</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.0179745583127</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.734167356327367</v>
+        <v>0.3809181092477624</v>
       </c>
       <c r="C2" t="n">
-        <v>10.36332876602933</v>
+        <v>16.02506777642068</v>
       </c>
       <c r="D2" t="n">
-        <v>15.30053797068654</v>
+        <v>7.844164156932014</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.385508052599507</v>
+        <v>1.821141991377833</v>
       </c>
       <c r="C3" t="n">
-        <v>23.81719930502762</v>
+        <v>23.80738182798515</v>
       </c>
       <c r="D3" t="n">
-        <v>75.71729169003525</v>
+        <v>29.22172041690631</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.52017171899734</v>
+        <v>6.432410958225102</v>
       </c>
       <c r="C4" t="n">
-        <v>69.96523189085319</v>
+        <v>83.08530821040756</v>
       </c>
       <c r="D4" t="n">
-        <v>177.542200079106</v>
+        <v>81.61759539255858</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.09429850399926</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="C5" t="n">
-        <v>159.288565014045</v>
+        <v>205.7988625027377</v>
       </c>
       <c r="D5" t="n">
-        <v>193.8706278961389</v>
+        <v>106.4459948329604</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.08313942635406</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="C6" t="n">
-        <v>278.7829685841498</v>
+        <v>332.3981742084766</v>
       </c>
       <c r="D6" t="n">
-        <v>122.0832722662036</v>
+        <v>87.50709987033521</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.64387192973244</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>313.6860629655323</v>
+        <v>380.2799732400019</v>
       </c>
       <c r="D7" t="n">
-        <v>59.6470635192192</v>
+        <v>51.56237117474672</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>235.9090645919873</v>
+        <v>278.0505847967816</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>120.2562397886003</v>
+        <v>127.2453016951333</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>24.29531043699581</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>47.54604131667303</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.21065915025234</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.516039439535327</v>
+        <v>3.499930565639879</v>
       </c>
       <c r="C2" t="n">
-        <v>5.998478472948011</v>
+        <v>18.0808474691135</v>
       </c>
       <c r="D2" t="n">
-        <v>12.54477216486574</v>
+        <v>13.79748223548467</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.97920337176157</v>
+        <v>0.3269219855141878</v>
       </c>
       <c r="C2" t="n">
-        <v>5.969026041820607</v>
+        <v>13.59622395611408</v>
       </c>
       <c r="D2" t="n">
-        <v>11.38336463074177</v>
+        <v>7.952156404399163</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.76272015520853</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C3" t="n">
-        <v>32.18168974521045</v>
+        <v>41.41502690365169</v>
       </c>
       <c r="D3" t="n">
-        <v>81.55869053030378</v>
+        <v>28.54922323949725</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.05767073930586</v>
+        <v>4.990223580686537</v>
       </c>
       <c r="C4" t="n">
-        <v>99.34501368814324</v>
+        <v>72.19870791801469</v>
       </c>
       <c r="D4" t="n">
-        <v>182.6983390218102</v>
+        <v>77.53352494289186</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.72303364087794</v>
+        <v>12.37002107350981</v>
       </c>
       <c r="C5" t="n">
-        <v>237.3865948868788</v>
+        <v>180.5434028109885</v>
       </c>
       <c r="D5" t="n">
-        <v>176.0519070640593</v>
+        <v>110.4711604203724</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.39500673447249</v>
+        <v>17.75098024048658</v>
       </c>
       <c r="C6" t="n">
-        <v>258.4961340235937</v>
+        <v>331.512637779246</v>
       </c>
       <c r="D6" t="n">
-        <v>93.98761646606842</v>
+        <v>97.20774893599796</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>13.89369351050086</v>
       </c>
       <c r="C7" t="n">
-        <v>165.8859095865836</v>
+        <v>421.1825278420368</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>61.8029814777452</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>88.62236526235957</v>
+        <v>374.1833199966293</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>36.27655941962388</v>
+        <v>213.7765443474471</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>26.5140602485936</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>88.54382544601984</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.92242623583128</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.280240064066846</v>
+        <v>3.147483139815274</v>
       </c>
       <c r="C2" t="n">
-        <v>7.791149780902686</v>
+        <v>11.53455377719578</v>
       </c>
       <c r="D2" t="n">
-        <v>31.01831871567797</v>
+        <v>17.92573133184251</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.601492547533805</v>
+        <v>5.649958037940394</v>
       </c>
       <c r="C3" t="n">
-        <v>15.11400590687965</v>
+        <v>35.70125526493526</v>
       </c>
       <c r="D3" t="n">
-        <v>13.67574552015807</v>
+        <v>12.41910845872215</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39804324627068</v>
+        <v>11.67673563185459</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14269699518178</v>
+        <v>59.94057624352025</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576240381914197</v>
+        <v>0.7784490421236396</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.587707021945345</v>
+        <v>2.085232123820225</v>
       </c>
       <c r="C2" t="n">
-        <v>3.794454876913922</v>
+        <v>8.786641953008953</v>
       </c>
       <c r="D2" t="n">
-        <v>23.73178725475815</v>
+        <v>18.03863231783089</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.81733817374786</v>
+        <v>9.012443924985719</v>
       </c>
       <c r="C3" t="n">
-        <v>24.66641106920111</v>
+        <v>41.86663084760523</v>
       </c>
       <c r="D3" t="n">
-        <v>36.42283982755666</v>
+        <v>25.07383636646354</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.28224461720434</v>
+        <v>7.121597846606362</v>
       </c>
       <c r="C4" t="n">
-        <v>23.59826956698058</v>
+        <v>57.64920694107695</v>
       </c>
       <c r="D4" t="n">
-        <v>22.23265851037327</v>
+        <v>20.80323385298991</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43840995984147</v>
+        <v>13.62416228333821</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13007661806292</v>
+        <v>73.73076059218326</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25019157049294</v>
+        <v>1.602842621569201</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.87535909928966</v>
+        <v>2.298271375641783</v>
       </c>
       <c r="C2" t="n">
-        <v>7.710646469154449</v>
+        <v>4.585743526536851</v>
       </c>
       <c r="D2" t="n">
-        <v>33.97436105316512</v>
+        <v>16.25872373003143</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.29701189049705</v>
+        <v>8.015970005175207</v>
       </c>
       <c r="C3" t="n">
-        <v>18.66302385773187</v>
+        <v>37.11006322052943</v>
       </c>
       <c r="D3" t="n">
-        <v>46.95699269412494</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.34301516387641</v>
+        <v>13.27322896141688</v>
       </c>
       <c r="C4" t="n">
-        <v>46.0606570401476</v>
+        <v>86.42914089107219</v>
       </c>
       <c r="D4" t="n">
-        <v>35.46759931132452</v>
+        <v>29.11176467403067</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.18563243156066</v>
+        <v>6.896777622333844</v>
       </c>
       <c r="C5" t="n">
-        <v>27.19441140763665</v>
+        <v>64.89352325071418</v>
       </c>
       <c r="D5" t="n">
-        <v>30.65507206510666</v>
+        <v>27.66074156715389</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.13430381349934</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72956338642046</v>
+        <v>14.82766602933231</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0503366571648</v>
+        <v>87.31847772829029</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182390846605114</v>
+        <v>2.471277671555386</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.33718143091316</v>
+        <v>2.106830573313655</v>
       </c>
       <c r="C2" t="n">
-        <v>4.202861921880595</v>
+        <v>3.289836556931061</v>
       </c>
       <c r="D2" t="n">
-        <v>30.62561963397925</v>
+        <v>15.851298432769</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46390900021901</v>
+        <v>8.05523991334508</v>
       </c>
       <c r="C3" t="n">
-        <v>25.15237618280328</v>
+        <v>25.59907138823558</v>
       </c>
       <c r="D3" t="n">
-        <v>62.33116174262999</v>
+        <v>39.24536447726624</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.54195009494002</v>
+        <v>14.5112128164721</v>
       </c>
       <c r="C4" t="n">
-        <v>46.41801320449344</v>
+        <v>90.21966877716913</v>
       </c>
       <c r="D4" t="n">
-        <v>50.18301565027996</v>
+        <v>39.69205968269854</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.55565350507047</v>
+        <v>13.71992416684918</v>
       </c>
       <c r="C5" t="n">
-        <v>58.4385320952914</v>
+        <v>118.0060740504666</v>
       </c>
       <c r="D5" t="n">
-        <v>35.9074222828271</v>
+        <v>31.98043146583985</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.821404033285093</v>
+        <v>7.003788122096746</v>
       </c>
       <c r="C6" t="n">
-        <v>28.13590745600934</v>
+        <v>60.0554705641859</v>
       </c>
       <c r="D6" t="n">
-        <v>38.40007970390975</v>
+        <v>33.16736444027425</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0504668646636</v>
+        <v>16.05921793303201</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7578076409006</v>
+        <v>100.5814175805689</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016822288221199</v>
+        <v>3.380887985901475</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.663121668723102</v>
+        <v>2.338523031515902</v>
       </c>
       <c r="C2" t="n">
-        <v>8.331111018238433</v>
+        <v>6.465790380169493</v>
       </c>
       <c r="D2" t="n">
-        <v>39.79907018246145</v>
+        <v>16.31173810606075</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.28857707178633</v>
+        <v>7.579092276785376</v>
       </c>
       <c r="C3" t="n">
-        <v>19.08517537055799</v>
+        <v>18.29486846863931</v>
       </c>
       <c r="D3" t="n">
-        <v>67.49515466696822</v>
+        <v>42.56367171762047</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.8242514654066</v>
+        <v>15.12382338392211</v>
       </c>
       <c r="C4" t="n">
-        <v>46.03513159983719</v>
+        <v>75.84884588240433</v>
       </c>
       <c r="D4" t="n">
-        <v>60.27832729304991</v>
+        <v>49.85118492624454</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.43860454408685</v>
+        <v>17.67145867644259</v>
       </c>
       <c r="C5" t="n">
-        <v>54.29064804484862</v>
+        <v>143.7769512869454</v>
       </c>
       <c r="D5" t="n">
-        <v>36.3982961349505</v>
+        <v>38.65631585471817</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.94845039776043</v>
+        <v>12.71952325622168</v>
       </c>
       <c r="C6" t="n">
-        <v>41.25794727097221</v>
+        <v>124.7398815538955</v>
       </c>
       <c r="D6" t="n">
-        <v>31.87931145230244</v>
+        <v>35.50196048097316</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>20.00212772632452</v>
+        <v>51.86180422454201</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>37.94062177832222</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.052949032062857</v>
+        <v>17.31308836517765</v>
       </c>
       <c r="C21" t="n">
-        <v>66.12139717558929</v>
+        <v>113.4007287919136</v>
       </c>
       <c r="D21" t="n">
-        <v>4.408093145039286</v>
+        <v>4.328272091294412</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.32794479094744</v>
+        <v>1.749474408967816</v>
       </c>
       <c r="C2" t="n">
-        <v>4.701589755637975</v>
+        <v>11.09374905798896</v>
       </c>
       <c r="D2" t="n">
-        <v>29.32676742126072</v>
+        <v>17.621389543526</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.92595231602077</v>
+        <v>7.701810739816228</v>
       </c>
       <c r="C3" t="n">
-        <v>27.76873381462103</v>
+        <v>21.79479903427919</v>
       </c>
       <c r="D3" t="n">
-        <v>84.6168346290326</v>
+        <v>45.00331476267379</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.20110371511713</v>
+        <v>14.81751810019711</v>
       </c>
       <c r="C4" t="n">
-        <v>47.23482729442679</v>
+        <v>59.69124216591032</v>
       </c>
       <c r="D4" t="n">
-        <v>81.08156114603983</v>
+        <v>57.77683414262904</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.02260555939346</v>
+        <v>19.95402208881642</v>
       </c>
       <c r="C5" t="n">
-        <v>73.18929135159972</v>
+        <v>141.7643684932394</v>
       </c>
       <c r="D5" t="n">
-        <v>51.32086123950202</v>
+        <v>46.80482179996669</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.76356303419254</v>
+        <v>17.99249017573129</v>
       </c>
       <c r="C6" t="n">
-        <v>67.78378849201678</v>
+        <v>174.6519348378034</v>
       </c>
       <c r="D6" t="n">
-        <v>36.74976181307086</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>11.0191362324662</v>
       </c>
       <c r="C7" t="n">
-        <v>43.05847256056086</v>
+        <v>111.5687543537203</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>39.1059563032632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>23.44904391593506</v>
+        <v>45.72980806381643</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.272112947759084</v>
+        <v>17.69830377250948</v>
       </c>
       <c r="C21" t="n">
-        <v>75.44817183300052</v>
+        <v>126.5428719734428</v>
       </c>
       <c r="D21" t="n">
-        <v>5.454084710819314</v>
+        <v>5.309491131752845</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.291219215262808</v>
+        <v>1.661117115585603</v>
       </c>
       <c r="C2" t="n">
-        <v>11.94983305609217</v>
+        <v>7.010660356026473</v>
       </c>
       <c r="D2" t="n">
-        <v>25.8386178280718</v>
+        <v>13.98794129010855</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.71349390127595</v>
+        <v>10.10218387669968</v>
       </c>
       <c r="C3" t="n">
-        <v>22.0991408225957</v>
+        <v>38.39615271309275</v>
       </c>
       <c r="D3" t="n">
-        <v>88.44565067559515</v>
+        <v>50.14767273292708</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.42931115085889</v>
+        <v>9.584802836561609</v>
       </c>
       <c r="C4" t="n">
-        <v>60.15070009149782</v>
+        <v>106.8622558595611</v>
       </c>
       <c r="D4" t="n">
-        <v>105.2796785603152</v>
+        <v>55.1732392309665</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.20194659410114</v>
+        <v>10.13654504634832</v>
       </c>
       <c r="C5" t="n">
-        <v>80.42968067041996</v>
+        <v>104.359780961436</v>
       </c>
       <c r="D5" t="n">
-        <v>68.32964021557801</v>
+        <v>36.71736413883072</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.61892732649877</v>
+        <v>6.84278149860027</v>
       </c>
       <c r="C6" t="n">
-        <v>94.59139130418019</v>
+        <v>73.45927197026759</v>
       </c>
       <c r="D6" t="n">
-        <v>44.88059629964295</v>
+        <v>25.72080810356219</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>73.00177754008857</v>
+        <v>32.15910954801276</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>26.94897448157494</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>41.47393176590651</v>
+        <v>23.11524969649115</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.06874770149305</v>
+        <v>25.62656032395449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.478776501289023</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.13623563950151</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.543929438627894</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
